--- a/ig/hospitalnotification/StructureDefinition-medcom-hospitalnotifiation-leave-period-extension.xlsx
+++ b/ig/hospitalnotification/StructureDefinition-medcom-hospitalnotifiation-leave-period-extension.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T09:56:15+01:00</t>
+    <t>2026-02-10T12:55:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -260,6 +260,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Extension.id</t>
   </si>
   <si>
@@ -305,10 +309,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Extension.url</t>
   </si>
   <si>
@@ -331,34 +331,35 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Period
 </t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>Extension.value[x]:valuePeriod.id</t>
@@ -558,10 +559,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -764,42 +765,42 @@
   <dimension ref="A1:AK11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.6640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.3828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.53125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.91015625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.9140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.07421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.7265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1012,7 +1013,7 @@
         <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>75</v>
@@ -1020,10 +1021,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1034,7 +1035,7 @@
         <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>75</v>
@@ -1046,13 +1047,13 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1103,13 +1104,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>75</v>
@@ -1118,15 +1119,15 @@
         <v>75</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1149,13 +1150,13 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>29</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1194,19 +1195,19 @@
         <v>75</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1218,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
@@ -1237,10 +1238,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>75</v>
@@ -1314,10 +1315,10 @@
         <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>75</v>
@@ -1345,7 +1346,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -1409,7 +1410,7 @@
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>101</v>
@@ -1418,27 +1419,27 @@
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>101</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -1448,19 +1449,19 @@
         <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>103</v>
@@ -1523,13 +1524,13 @@
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>100</v>
@@ -1551,7 +1552,7 @@
         <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>75</v>
@@ -1563,13 +1564,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1620,13 +1621,13 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>75</v>
@@ -1635,7 +1636,7 @@
         <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" hidden="true">
@@ -1666,7 +1667,7 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>116</v>
@@ -1713,19 +1714,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1737,13 +1738,13 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" hidden="true">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>119</v>
       </c>
@@ -1756,19 +1757,19 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>121</v>
@@ -1836,19 +1837,19 @@
         <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>128</v>
       </c>
@@ -1864,16 +1865,16 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>121</v>
@@ -1943,13 +1944,13 @@
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>135</v>
@@ -1957,12 +1958,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK11">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
